--- a/etl/data/inputs/Shell Tank Cleanning Data.xlsx
+++ b/etl/data/inputs/Shell Tank Cleanning Data.xlsx
@@ -26,11 +26,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="266">
   <si>
     <t xml:space="preserve">UN No</t>
   </si>
   <si>
+    <t xml:space="preserve">Aggregated Name</t>
+  </si>
+  <si>
     <t xml:space="preserve">Matrix Title</t>
   </si>
   <si>
@@ -55,6 +58,9 @@
     <t xml:space="preserve">1202</t>
   </si>
   <si>
+    <t xml:space="preserve">AD10 - 10ppm Diesel fuel, ADO, AGO</t>
+  </si>
+  <si>
     <t xml:space="preserve">ULSD – 10ppm</t>
   </si>
   <si>
@@ -76,6 +82,9 @@
     <t xml:space="preserve">Straw, amber, lime coloured liquid. Water sensitive and highly sulphur sensitive cargo. May contain FAME</t>
   </si>
   <si>
+    <t xml:space="preserve">ULSD - 50ppm Diesel fuel, ADO, AGO</t>
+  </si>
+  <si>
     <t xml:space="preserve">ULSD - 50ppm</t>
   </si>
   <si>
@@ -89,6 +98,9 @@
   </si>
   <si>
     <t xml:space="preserve">Straw, amber, lime, coloured liquid. Water sensitive &amp; sulphur sensitive cargo. May contain FAME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detergent Addivated, 10ppm Diesel fuel, V-Power Diesel</t>
   </si>
   <si>
     <t xml:space="preserve">V-Power Diesel</t>
@@ -104,6 +116,9 @@
     <t xml:space="preserve">1223/1202</t>
   </si>
   <si>
+    <t xml:space="preserve">GTL Kero &amp; Diesel, Synthetic Distillate</t>
+  </si>
+  <si>
     <t xml:space="preserve">GTL Kero &amp; Diesel</t>
   </si>
   <si>
@@ -140,6 +155,9 @@
     <t xml:space="preserve">Colourless, low odour liquids. High quality drilling fluid. Very sensitive to flash, sulphur and aromatics.</t>
   </si>
   <si>
+    <t xml:space="preserve">2000 ppm Gasoil undyed, IGO, GOCI</t>
+  </si>
+  <si>
     <t xml:space="preserve">2000ppm Gasoil Un-Dyed</t>
   </si>
   <si>
@@ -161,6 +179,9 @@
     <t xml:space="preserve">Diesel/Process gas oil – straw, amber, lime green or gold coloured liquid. Water sensitive cargo.</t>
   </si>
   <si>
+    <t xml:space="preserve">Gas Oil 2000 ppm, Gasoil dyed, IGO, GOCI</t>
+  </si>
+  <si>
     <t xml:space="preserve">2000ppm Gasoil Dyed</t>
   </si>
   <si>
@@ -170,6 +191,9 @@
     <t xml:space="preserve">1203</t>
   </si>
   <si>
+    <t xml:space="preserve">10 ppm Gasoline,PU10, SU10, ULG</t>
+  </si>
+  <si>
     <t xml:space="preserve">10ppm Gasoline</t>
   </si>
   <si>
@@ -188,6 +212,9 @@
     <t xml:space="preserve">Amber or lime green, highly flammable and volatile liquid. No lead allowed, Highly Sulphur Sensitive.</t>
   </si>
   <si>
+    <t xml:space="preserve">50 ppm Gasoline, PU50, SU50, ULG</t>
+  </si>
+  <si>
     <t xml:space="preserve">50ppm Gasoline</t>
   </si>
   <si>
@@ -203,6 +230,9 @@
     <t xml:space="preserve">1863</t>
   </si>
   <si>
+    <t xml:space="preserve">Jet A1, AVTUR, Aviation Fuel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jet A1</t>
   </si>
   <si>
@@ -227,6 +257,9 @@
     <t xml:space="preserve">1223</t>
   </si>
   <si>
+    <t xml:space="preserve">Kerosene, Class C2 Burning Oil</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kerosene</t>
   </si>
   <si>
@@ -234,6 +267,9 @@
   </si>
   <si>
     <t xml:space="preserve">Colourless to pale yellow liquid. Odour and colour sensitive product. May or may not be Customs Marked with</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVGAS, 100LL, Aviation Fuel</t>
   </si>
   <si>
     <t xml:space="preserve">AVGAS</t>
@@ -258,6 +294,9 @@
     <t xml:space="preserve">2398 &amp; 1149</t>
   </si>
   <si>
+    <t xml:space="preserve">MTBE &amp; ETBE, Methyl &amp; Ethyl Tertiary Butyl Ether </t>
+  </si>
+  <si>
     <t xml:space="preserve">MTBE &amp; ETBE</t>
   </si>
   <si>
@@ -279,6 +318,9 @@
     <t xml:space="preserve">1307 &amp; 1294</t>
   </si>
   <si>
+    <t xml:space="preserve">Xylene, Xylenes-C8</t>
+  </si>
+  <si>
     <t xml:space="preserve">Xylenes-C8 &amp; Toluene</t>
   </si>
   <si>
@@ -303,6 +345,9 @@
     <t xml:space="preserve">3295</t>
   </si>
   <si>
+    <t xml:space="preserve">Benzene Heart Cut, BHC, HCB</t>
+  </si>
+  <si>
     <t xml:space="preserve">Benzene Heart Cut</t>
   </si>
   <si>
@@ -319,6 +364,9 @@
   </si>
   <si>
     <t xml:space="preserve">Clear colourless volatile liquid, with approx 30 to 60% benzene. Water, sulphur &amp; oxygenate sensitive cargo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natural Gas Condensate (crude feedstock)</t>
   </si>
   <si>
     <t xml:space="preserve">Nat Gas Condensate</t>
@@ -341,6 +389,9 @@
 test. May contain up to 10% Benzene.</t>
   </si>
   <si>
+    <t xml:space="preserve">PyGas, Pygas-tail, Pyrolysis Gasoline</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pygas</t>
   </si>
   <si>
@@ -368,6 +419,9 @@
     <t xml:space="preserve">Pale yellow coloured volatile liquid, rich in aromatics &amp; benzene.</t>
   </si>
   <si>
+    <t xml:space="preserve">Cat Cracked Gasoline. LCCG, FRCCG</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cat Cracked Gasoline</t>
   </si>
   <si>
@@ -386,6 +440,9 @@
     <t xml:space="preserve">Pale yellow to yellow coloured liquid, pungent gasoline odour, rich in olefins. Sulphur &amp; oxygenate sensitive</t>
   </si>
   <si>
+    <t xml:space="preserve">Platformate, Reformate - Mogas or Chem</t>
+  </si>
+  <si>
     <t xml:space="preserve">Platformate / Reformate</t>
   </si>
   <si>
@@ -401,6 +458,9 @@
     <t xml:space="preserve">1268</t>
   </si>
   <si>
+    <t xml:space="preserve">Naphtha, Naphtha platfeed</t>
+  </si>
+  <si>
     <t xml:space="preserve">Naphtha</t>
   </si>
   <si>
@@ -413,6 +473,9 @@
     <t xml:space="preserve">Clear, virtually colourless, volatile liquid. As these grades are used as feedstock's they may put other grades off-</t>
   </si>
   <si>
+    <t xml:space="preserve">Isomerate, Gasoline component</t>
+  </si>
+  <si>
     <t xml:space="preserve">Isomerate</t>
   </si>
   <si>
@@ -425,6 +488,9 @@
     <t xml:space="preserve">Colourless/pale yellow, volatile liquid</t>
   </si>
   <si>
+    <t xml:space="preserve">Alkylate, Gasoline component</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alkylate</t>
   </si>
   <si>
@@ -438,6 +504,9 @@
   </si>
   <si>
     <t xml:space="preserve">Colourless volatile liquid with a sweet odour,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAME, Fatty Acid Methyl Esters</t>
   </si>
   <si>
     <t xml:space="preserve">FAME</t>
@@ -463,6 +532,9 @@
     <t xml:space="preserve">1170/1230</t>
   </si>
   <si>
+    <t xml:space="preserve">Ethanol, 100% EtOH, Ethyl Alcohol</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ethanol/Methanol</t>
   </si>
   <si>
@@ -480,6 +552,9 @@
     <t xml:space="preserve">Colourless volatile &amp; toxic liquid. Completely water soluble. Water, salt and sulphur sensitive cargo.</t>
   </si>
   <si>
+    <t xml:space="preserve">Cycle Oil, Gas Oil &amp; Cutter Stock</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cycle Oil</t>
   </si>
   <si>
@@ -499,6 +574,9 @@
   </si>
   <si>
     <t xml:space="preserve">A heavy cat cracked component, mildly viscous, pale yellow to dark brown colour. Water sensitive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vegetable Oils, MO, RO, PO, TO</t>
   </si>
   <si>
     <t xml:space="preserve">Veg Oil</t>
@@ -517,6 +595,9 @@
   <si>
     <t xml:space="preserve">Pale yellow to amber/dark brown coloured viscous liquid. Water sensitive cargo. Cleaning regimes will change
 with the specific grade discharged. Can form lacquers on heating.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lube Base Oil ((not a finished Lubricant)</t>
   </si>
   <si>
     <t xml:space="preserve">Lubricant Base Oils</t>
@@ -766,7 +847,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -797,18 +878,31 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -852,7 +946,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -867,6 +961,22 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -915,17 +1025,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H1048576"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I30"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="35.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="31.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="35.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="55"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -953,745 +1064,828 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>23</v>
+        <v>16</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="2" t="n">
         <v>800</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>34</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>32</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B6" s="5"/>
       <c r="C6" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="0" t="n">
         <v>85</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="G6" s="0" t="n">
         <v>780</v>
       </c>
-      <c r="G6" s="0" t="s">
-        <v>35</v>
-      </c>
       <c r="H6" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
+      </c>
+      <c r="I6" s="0" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="E8" s="2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>52</v>
+        <v>16</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="B10" s="3" t="s">
+        <v>61</v>
+      </c>
       <c r="C10" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>56</v>
+        <v>22</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>58</v>
+        <v>66</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>64</v>
+        <v>73</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>68</v>
+        <v>48</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>69</v>
+        <v>53</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>76</v>
+        <v>87</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>89</v>
+        <v>102</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>91</v>
+        <v>104</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>96</v>
+        <v>110</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="n">
         <v>1993</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>97</v>
+      <c r="B17" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>102</v>
+        <v>117</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>109</v>
+      <c r="B19" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>111</v>
+        <v>124</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>129</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>117</v>
+        <v>134</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>118</v>
+        <v>104</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>136</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>50</v>
+        <v>139</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>121</v>
+        <v>93</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>123</v>
+        <v>141</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>142</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I22" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="n">
         <v>1268</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>127</v>
+      <c r="B23" s="3" t="s">
+        <v>147</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F23" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23" s="2" t="n">
         <v>700</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="H23" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>150</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="n">
         <v>3295</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>131</v>
+      <c r="B24" s="3" t="s">
+        <v>152</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="F24" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G24" s="2" t="n">
         <v>700</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="H24" s="2" t="s">
-        <v>135</v>
+        <v>150</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>137</v>
+        <v>36</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>159</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>14</v>
+        <v>163</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>16</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
+      <c r="B26" s="6"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>143</v>
+        <v>165</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>166</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>86</v>
+        <v>170</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>147</v>
+        <v>100</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>148</v>
+        <v>9</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>172</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>154</v>
+        <v>178</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>155</v>
+        <v>36</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>180</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>14</v>
+        <v>163</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>159</v>
+        <v>16</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="n">
         <v>1202</v>
       </c>
-      <c r="B30" s="0" t="s">
-        <v>160</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="E30" s="0" t="s">
-        <v>163</v>
+      <c r="B30" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>189</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>164</v>
-      </c>
-      <c r="H30" s="0" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>190</v>
+      </c>
+      <c r="G30" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="I30" s="0" t="s">
+        <v>192</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1709,7 +1903,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
@@ -1722,184 +1916,184 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>196</v>
+        <v>223</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>198</v>
+        <v>225</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -1921,7 +2115,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19"/>
@@ -1930,200 +2124,200 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>205</v>
+        <v>232</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>206</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>208</v>
+        <v>235</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>209</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>212</v>
+        <v>239</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>213</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>214</v>
+        <v>241</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>215</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>216</v>
+        <v>243</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>217</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>219</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>220</v>
+        <v>247</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>223</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>225</v>
+        <v>252</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>226</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>227</v>
+        <v>254</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>229</v>
+        <v>256</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>230</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>232</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>235</v>
+        <v>262</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>238</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
